--- a/du_lieu_test/TEST_02_chon_CLB_muon_thi.xlsx
+++ b/du_lieu_test/TEST_02_chon_CLB_muon_thi.xlsx
@@ -431,16 +431,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G121"/>
+  <dimension ref="A1:M121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -466,17 +472,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>score_1</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>test_club_2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>score_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>test_club_3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>score_3</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>test_club_4</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>score_4</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>test_club_5</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>score_5</t>
         </is>
       </c>
     </row>
@@ -494,24 +530,26 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>clb_bongro</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>clb_robotics</t>
-        </is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>7.9</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -531,24 +569,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>clb_amnhac</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>clb_tienganh</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>clb_vanhoc</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>clb_bongda</t>
-        </is>
-      </c>
+      <c r="K3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -568,24 +620,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>clb_tienganh</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>clb_mythuat</t>
-        </is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6.7</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>clb_robotics</t>
-        </is>
-      </c>
+          <t>clb_bongro</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -604,20 +658,40 @@
           <t>clb_bongda</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>clb_vanhoc</t>
-        </is>
+      <c r="E5" t="n">
+        <v>8.9</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>clb_mythuat</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>clb_tinhnguyen</t>
-        </is>
+      <c r="G5" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>7</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>clb_bongro</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>7.5</v>
       </c>
     </row>
     <row r="6">
@@ -634,16 +708,32 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>clb_bongda</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>clb_amnhac</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -659,16 +749,32 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>clb_tienganh</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>clb_khoahoc</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -684,16 +790,44 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>clb_tinhnguyen</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>clb_vanhoc</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>8.9</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -709,16 +843,32 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>clb_tinhoc</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>clb_tinhnguyen</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -734,24 +884,32 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>clb_tinhnguyen</t>
-        </is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>9.1</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>clb_vanhoc</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>clb_khoahoc</t>
-        </is>
-      </c>
+      <c r="G10" t="n">
+        <v>7</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -767,24 +925,38 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>clb_khoahoc</t>
-        </is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>9.300000000000001</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>clb_tinhnguyen</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>clb_bongro</t>
-        </is>
-      </c>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>7</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -800,20 +972,32 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>clb_tinhnguyen</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>clb_tienganh</t>
-        </is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6.4</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>clb_bongda</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>clb_vanhoc</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -829,16 +1013,38 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>clb_bongro</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>clb_vanhoc</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>7</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -854,24 +1060,38 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>clb_tinhnguyen</t>
-        </is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5.1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>clb_amnhac</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>clb_tinhoc</t>
-        </is>
-      </c>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -891,20 +1111,44 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>clb_tienganh</t>
-        </is>
+          <t>clb_bongro</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4.5</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>clb_bongda</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>6</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>clb_amnhac</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>6.3</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -920,20 +1164,26 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>clb_bongro</t>
-        </is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>7.1</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>clb_amnhac</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -949,20 +1199,38 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>clb_tinhnguyen</t>
-        </is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>9</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>clb_bongda</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -978,16 +1246,38 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>clb_bongda</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>clb_khoahoc</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1003,20 +1293,26 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>clb_tinhnguyen</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>clb_vanhoc</t>
-        </is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>7.4</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1032,16 +1328,32 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>clb_bongro</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>clb_bongda</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1057,16 +1369,32 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>clb_bongro</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>clb_bongda</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
+          <t>clb_robotics</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>8</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1086,20 +1414,32 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>clb_tienganh</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>clb_robotics</t>
-        </is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6.9</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>clb_amnhac</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1122,17 +1462,23 @@
           <t>clb_tinhoc</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>clb_mythuat</t>
-        </is>
+      <c r="E23" t="n">
+        <v>6.2</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>clb_tinhnguyen</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>4</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1155,17 +1501,23 @@
           <t>clb_tinhoc</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>clb_tienganh</t>
-        </is>
+      <c r="E24" t="n">
+        <v>5.9</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
+          <t>clb_robotics</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1185,24 +1537,26 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>clb_vanhoc</t>
-        </is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6.7</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>clb_bongro</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>clb_tinhoc</t>
-        </is>
-      </c>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1218,16 +1572,44 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>clb_tinhoc</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>clb_khoahoc</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>clb_vanhoc</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>8</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>clb_amnhac</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1243,20 +1625,26 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>clb_tinhnguyen</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>clb_bongro</t>
-        </is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>7.9</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>clb_amnhac</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1272,16 +1660,26 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>clb_tinhnguyen</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>clb_amnhac</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>9</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1297,24 +1695,32 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>clb_tienganh</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>clb_vanhoc</t>
-        </is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>7.2</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>clb_khoahoc</t>
-        </is>
-      </c>
+          <t>clb_bongro</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>clb_amnhac</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1330,16 +1736,44 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>clb_tinhoc</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>clb_tinhnguyen</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>clb_bongro</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>8</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>8.300000000000001</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1355,16 +1789,38 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>clb_robotics</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>8</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>clb_tinhnguyen</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>clb_amnhac</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1380,16 +1836,32 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>clb_tinhoc</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>clb_khoahoc</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>clb_bongro</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>7</v>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1405,24 +1877,26 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>clb_bongro</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>clb_amnhac</t>
-        </is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>7.6</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1438,16 +1912,38 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>clb_bongda</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>clb_robotics</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>clb_bongro</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>7</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1463,20 +1959,38 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>clb_bongda</t>
-        </is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>clb_tienganh</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
+          <t>clb_amnhac</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>clb_tinhnguyen</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>10</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1492,16 +2006,32 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
           <t>clb_amnhac</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
+      <c r="E36" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1524,17 +2054,41 @@
           <t>clb_bongda</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>clb_tinhoc</t>
-        </is>
+      <c r="E37" t="n">
+        <v>6.5</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>clb_bongro</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr"/>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>clb_amnhac</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>6.4</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1550,16 +2104,26 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>clb_tienganh</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1575,23 +2139,43 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>clb_amnhac</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>clb_mythuat</t>
-        </is>
+          <t>clb_robotics</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>7.7</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>clb_tinhnguyen</t>
-        </is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>clb_khoahoc</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="40">
@@ -1608,24 +2192,32 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>clb_tienganh</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>clb_khoahoc</t>
-        </is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>8.6</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>clb_tinhoc</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
+          <t>clb_bongro</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>10</v>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1644,17 +2236,29 @@
           <t>clb_tienganh</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>clb_vanhoc</t>
-        </is>
+      <c r="E41" t="n">
+        <v>7.1</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>clb_bongda</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1670,16 +2274,38 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
+          <t>clb_bongro</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>clb_amnhac</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1695,20 +2321,44 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>clb_bongda</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>clb_bongro</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>clb_robotics</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>7</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>6.6</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1724,16 +2374,26 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>clb_tienganh</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
+          <t>clb_bongro</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>8</v>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1749,16 +2409,38 @@
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
           <t>clb_bongro</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>clb_amnhac</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
+      <c r="I45" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>clb_robotics</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1774,24 +2456,38 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>clb_bongda</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>clb_tinhoc</t>
-        </is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>7.5</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1807,16 +2503,32 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>clb_tinhnguyen</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>clb_khoahoc</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>clb_robotics</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1832,16 +2544,32 @@
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>clb_robotics</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>clb_bongro</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1857,24 +2585,26 @@
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>clb_bongro</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
           <t>clb_vanhoc</t>
         </is>
       </c>
+      <c r="E49" t="n">
+        <v>7.5</v>
+      </c>
       <c r="F49" t="inlineStr">
         <is>
           <t>clb_bongda</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>clb_tinhnguyen</t>
-        </is>
-      </c>
+      <c r="G49" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1890,20 +2620,38 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>clb_vanhoc</t>
-        </is>
+          <t>clb_bongro</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>8.4</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
+          <t>clb_tinhnguyen</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1923,24 +2671,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>clb_tinhnguyen</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>clb_mythuat</t>
-        </is>
+          <t>clb_amnhac</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6.5</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>clb_tienganh</t>
-        </is>
-      </c>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>7</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1956,16 +2718,38 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>clb_tinhoc</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>clb_tinhnguyen</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>clb_bongro</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>10</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1981,20 +2765,44 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>clb_tinhoc</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>clb_amnhac</t>
-        </is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>10</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>clb_tienganh</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr"/>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>clb_vanhoc</t>
+        </is>
+      </c>
+      <c r="M53" t="n">
+        <v>7.9</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2010,24 +2818,26 @@
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>clb_amnhac</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>clb_khoahoc</t>
-        </is>
+          <t>clb_tinhnguyen</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>7.2</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
           <t>clb_mythuat</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>clb_bongda</t>
-        </is>
-      </c>
+      <c r="G54" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2043,20 +2853,32 @@
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>clb_tinhoc</t>
-        </is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>8.6</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>clb_tienganh</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr"/>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2072,16 +2894,44 @@
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>clb_tienganh</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>clb_amnhac</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="M56" t="n">
+        <v>6.9</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2097,16 +2947,38 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>clb_bongro</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2122,23 +2994,43 @@
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>clb_bongro</t>
-        </is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6.6</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
           <t>clb_amnhac</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>clb_tinhnguyen</t>
-        </is>
+      <c r="G58" t="n">
+        <v>8</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>clb_khoahoc</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="M58" t="n">
+        <v>6.7</v>
       </c>
     </row>
     <row r="59">
@@ -2159,24 +3051,32 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>clb_tinhnguyen</t>
-        </is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>8.5</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2196,16 +3096,26 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>clb_khoahoc</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
+          <t>clb_amnhac</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2221,20 +3131,44 @@
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>clb_tinhoc</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>clb_khoahoc</t>
-        </is>
+          <t>clb_amnhac</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6.6</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr"/>
+          <t>clb_vanhoc</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>clb_tinhnguyen</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="M61" t="n">
+        <v>6.4</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2250,16 +3184,38 @@
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2279,16 +3235,26 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>clb_khoahoc</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2307,21 +3273,35 @@
           <t>clb_bongda</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>clb_tinhnguyen</t>
-        </is>
+      <c r="E64" t="n">
+        <v>8.6</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>clb_vanhoc</t>
-        </is>
-      </c>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>5</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>clb_amnhac</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>9</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2337,24 +3317,26 @@
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>clb_bongda</t>
-        </is>
+          <t>clb_amnhac</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>7.3</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
           <t>clb_mythuat</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>clb_tinhnguyen</t>
-        </is>
-      </c>
+      <c r="G65" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2374,20 +3356,32 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>clb_tienganh</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>clb_vanhoc</t>
-        </is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
           <t>clb_mythuat</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
+      <c r="G66" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2403,16 +3397,26 @@
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>clb_vanhoc</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
+          <t>clb_tinhnguyen</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2432,16 +3436,44 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>clb_bongda</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>clb_amnhac</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
+          <t>clb_vanhoc</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="M68" t="n">
+        <v>7.4</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2457,16 +3489,32 @@
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>clb_robotics</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>clb_bongro</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2482,20 +3530,26 @@
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>clb_bongda</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>clb_vanhoc</t>
-        </is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>8.1</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr"/>
+          <t>clb_amnhac</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2511,24 +3565,32 @@
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>clb_bongda</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>clb_bongro</t>
-        </is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>7.9</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>clb_tinhnguyen</t>
-        </is>
-      </c>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>clb_amnhac</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2544,24 +3606,32 @@
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>clb_tinhoc</t>
-        </is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>9.5</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>clb_bongro</t>
-        </is>
-      </c>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2581,24 +3651,32 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>clb_tinhnguyen</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>clb_robotics</t>
-        </is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>9.6</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>8</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>clb_bongro</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2617,13 +3695,35 @@
           <t>clb_mythuat</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>clb_bongda</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
+      <c r="E74" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2643,24 +3743,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>clb_tinhnguyen</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>clb_robotics</t>
-        </is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6.7</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>clb_tinhoc</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
           <t>clb_amnhac</t>
         </is>
       </c>
+      <c r="G75" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2680,24 +3794,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>clb_tinhnguyen</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>clb_robotics</t>
-        </is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>clb_tienganh</t>
-        </is>
-      </c>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>clb_khoahoc</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2713,24 +3841,26 @@
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>clb_tienganh</t>
-        </is>
+          <t>clb_tinhnguyen</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6.9</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>clb_amnhac</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2749,13 +3879,41 @@
           <t>clb_bongro</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>clb_tinhoc</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
+      <c r="E78" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="M78" t="n">
+        <v>8.199999999999999</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2771,24 +3929,38 @@
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>clb_bongda</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>clb_amnhac</t>
-        </is>
+          <t>clb_khoahoc</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6.7</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>clb_khoahoc</t>
-        </is>
-      </c>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>10</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>7</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2804,24 +3976,26 @@
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>clb_bongda</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>clb_amnhac</t>
-        </is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
           <t>clb_mythuat</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>clb_vanhoc</t>
-        </is>
-      </c>
+      <c r="G80" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2837,20 +4011,26 @@
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>clb_bongro</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>clb_amnhac</t>
-        </is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>9.800000000000001</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
           <t>clb_mythuat</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
+      <c r="G81" t="n">
+        <v>8</v>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2866,20 +4046,26 @@
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>clb_bongro</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>clb_amnhac</t>
-        </is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>8.5</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr"/>
+          <t>clb_vanhoc</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2895,24 +4081,32 @@
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>clb_khoahoc</t>
-        </is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>5.9</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>clb_bongro</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>clb_vanhoc</t>
-        </is>
-      </c>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2932,24 +4126,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>clb_bongro</t>
-        </is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>5.9</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>clb_tinhoc</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>clb_bongda</t>
-        </is>
-      </c>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>clb_khoahoc</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>6</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2965,20 +4173,26 @@
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>clb_tinhnguyen</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>clb_khoahoc</t>
-        </is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>7.1</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr"/>
+          <t>clb_robotics</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2994,16 +4208,44 @@
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>clb_tinhoc</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>clb_amnhac</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>clb_bongro</t>
+        </is>
+      </c>
+      <c r="M86" t="n">
+        <v>8.4</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3019,16 +4261,32 @@
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>clb_bongda</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>clb_tinhnguyen</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>clb_vanhoc</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3044,24 +4302,32 @@
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>clb_bongro</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>clb_robotics</t>
-        </is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>7.4</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>clb_tienganh</t>
-        </is>
-      </c>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>6</v>
+      </c>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3077,16 +4343,38 @@
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
           <t>clb_robotics</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>clb_khoahoc</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
+      <c r="K89" t="n">
+        <v>9</v>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3105,21 +4393,29 @@
           <t>clb_bongro</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>clb_bongda</t>
-        </is>
+      <c r="E90" t="n">
+        <v>7.2</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>clb_robotics</t>
-        </is>
-      </c>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>8</v>
+      </c>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3135,16 +4431,32 @@
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
           <t>clb_bongro</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>clb_robotics</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
+      <c r="G91" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>clb_amnhac</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>8</v>
+      </c>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3160,20 +4472,32 @@
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>clb_tinhoc</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>clb_robotics</t>
-        </is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>8</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr"/>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3189,23 +4513,43 @@
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>clb_vanhoc</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
           <t>clb_robotics</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>clb_bongro</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>clb_bongda</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>clb_vanhoc</t>
-        </is>
+      <c r="M93" t="n">
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="94">
@@ -3226,16 +4570,44 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>clb_bongro</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H94" t="inlineStr">
         <is>
           <t>clb_amnhac</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
+      <c r="I94" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>clb_robotics</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="M94" t="n">
+        <v>6.8</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3254,13 +4626,29 @@
           <t>clb_tinhoc</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>clb_amnhac</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
+      <c r="E95" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3279,21 +4667,35 @@
           <t>clb_bongda</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>clb_tinhoc</t>
-        </is>
+      <c r="E96" t="n">
+        <v>7.8</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
           <t>clb_vanhoc</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>clb_robotics</t>
-        </is>
-      </c>
+      <c r="K96" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3313,20 +4715,26 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>clb_bongda</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>clb_mythuat</t>
-        </is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>6.7</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr"/>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3342,16 +4750,32 @@
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>clb_tienganh</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>clb_amnhac</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>clb_bongro</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3367,24 +4791,26 @@
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>clb_khoahoc</t>
-        </is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>7.6</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>clb_bongro</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>clb_tinhnguyen</t>
-        </is>
-      </c>
+          <t>clb_vanhoc</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3400,16 +4826,32 @@
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>clb_tienganh</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="I100" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3432,21 +4874,23 @@
           <t>clb_bongda</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>clb_tinhoc</t>
-        </is>
+      <c r="E101" t="n">
+        <v>6.7</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>clb_bongro</t>
-        </is>
-      </c>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3466,20 +4910,32 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>clb_tienganh</t>
-        </is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>5</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>clb_bongro</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr"/>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3495,16 +4951,26 @@
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>clb_tinhoc</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>clb_tinhnguyen</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>clb_vanhoc</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3524,16 +4990,26 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>clb_bongro</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>clb_amnhac</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3549,24 +5025,26 @@
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>clb_amnhac</t>
-        </is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>7.7</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>clb_tinhoc</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>clb_bongro</t>
-        </is>
-      </c>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3582,20 +5060,26 @@
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
           <t>clb_bongro</t>
         </is>
       </c>
+      <c r="E106" t="n">
+        <v>8.1</v>
+      </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>clb_amnhac</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr"/>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3611,20 +5095,32 @@
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>clb_tinhnguyen</t>
-        </is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>7.6</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
+          <t>clb_vanhoc</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
           <t>clb_amnhac</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
+      <c r="I107" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3640,16 +5136,38 @@
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>clb_vanhoc</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>clb_amnhac</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>clb_robotics</t>
+        </is>
+      </c>
+      <c r="I108" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="K108" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3665,16 +5183,32 @@
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>clb_tienganh</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>clb_amnhac</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="I109" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3694,24 +5228,32 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>clb_amnhac</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>clb_bongda</t>
-        </is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>6.3</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>clb_bongro</t>
-        </is>
-      </c>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="I110" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3727,20 +5269,44 @@
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>clb_tinhoc</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>clb_vanhoc</t>
-        </is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>8.699999999999999</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>clb_amnhac</t>
+        </is>
+      </c>
+      <c r="I111" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>clb_robotics</t>
+        </is>
+      </c>
+      <c r="K111" t="n">
+        <v>9</v>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
           <t>clb_bongro</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
+      <c r="M111" t="n">
+        <v>8.6</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3756,24 +5322,26 @@
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>clb_amnhac</t>
-        </is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>6.4</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>clb_tienganh</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>clb_tinhoc</t>
-        </is>
-      </c>
+          <t>clb_tinhnguyen</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3789,20 +5357,44 @@
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>clb_tinhnguyen</t>
-        </is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>6.8</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr"/>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="I113" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="K113" t="n">
+        <v>7</v>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>clb_amnhac</t>
+        </is>
+      </c>
+      <c r="M113" t="n">
+        <v>8.6</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3818,20 +5410,44 @@
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
-          <t>clb_tinhoc</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>clb_khoahoc</t>
-        </is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>8.1</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr"/>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>9</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>clb_tinhnguyen</t>
+        </is>
+      </c>
+      <c r="I114" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>clb_amnhac</t>
+        </is>
+      </c>
+      <c r="K114" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="M114" t="n">
+        <v>4.4</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3847,16 +5463,32 @@
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
-          <t>clb_amnhac</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>clb_khoahoc</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>clb_tinhnguyen</t>
+        </is>
+      </c>
+      <c r="I115" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3872,24 +5504,32 @@
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>clb_tienganh</t>
-        </is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>6.7</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
           <t>clb_bongda</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>clb_tinhoc</t>
-        </is>
-      </c>
+      <c r="G116" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="I116" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3905,24 +5545,32 @@
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>clb_vanhoc</t>
-        </is>
+          <t>clb_amnhac</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>7.6</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>clb_bongro</t>
-        </is>
-      </c>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="I117" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3942,23 +5590,43 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>clb_bongro</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>clb_robotics</t>
-        </is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>5.9</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>clb_tienganh</t>
-        </is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>clb_amnhac</t>
+        </is>
+      </c>
+      <c r="I118" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>clb_tinhnguyen</t>
+        </is>
+      </c>
+      <c r="K118" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="M118" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="119">
@@ -3975,20 +5643,26 @@
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
-          <t>clb_bongda</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>clb_tinhnguyen</t>
-        </is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>9.199999999999999</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr"/>
+          <t>clb_bongro</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>7</v>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4004,16 +5678,38 @@
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
-          <t>clb_tinhoc</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>clb_amnhac</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>clb_robotics</t>
+        </is>
+      </c>
+      <c r="I120" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="K120" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4033,20 +5729,32 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>clb_tinhnguyen</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>clb_robotics</t>
-        </is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>5.6</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>clb_bongro</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr"/>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4059,7 +5767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="82" customWidth="1" min="1" max="1"/>
@@ -4078,7 +5786,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>120 học sinh, mỗi em đăng ký thi 2-4 CLB.</t>
+          <t>120 học sinh, mỗi em đăng ký thi 2-5 CLB.</t>
         </is>
       </c>
     </row>
@@ -4088,39 +5796,63 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cột reserve_group: khoảng 22%% số em thuộc diện dự trữ</t>
+          <t>Cột score_1 đi kèm test_club_1, score_2 đi kèm test_club_2, và</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>(chinh_sach hoặc khoi_10), phần còn lại để trống.</t>
+          <t>cứ thế — GHÉP THEO SỐ THỨ TỰ trong tên cột, không theo vị trí.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Nạp file này là có luôn điểm chấm, không phải gõ tay 400 ô.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Ô trống ở các cột test_club_* là bình thường — không cần điền kín.</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Cột reserve_group: khoảng 22%% số em thuộc diện dự trữ</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>(chinh_sach hoặc khoi_10), phần còn lại để trống.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ô trống ở các cột test_club_* và score_* là bình thường.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Sinh bằng du_lieu_test/tao_du_lieu_test.py, seed = 2026</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Chạy lại script luôn cho ra đúng bộ dữ liệu này.</t>
         </is>
